--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -503,7 +503,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
@@ -575,12 +575,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Sin actividades (semana mechona)</t>
+          <t>Repaso (semana mechona)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -871,12 +871,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Sin actividades (semana mechona)</t>
+          <t>Repaso (semana mechona)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">

--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,11 +59,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,19 +109,18 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -503,10 +497,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,12 +569,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -615,12 +609,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -655,12 +649,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -695,12 +689,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -713,21 +707,13 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Control lógica 2, 15 min</t>
-        </is>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -743,12 +729,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -783,12 +769,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -801,21 +787,13 @@
           <t>Lógica 3</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Control lógica 3, 15 min</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -831,12 +809,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -846,7 +824,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Modelos y Derivadas 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -871,12 +849,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -886,7 +864,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Repaso (semana mechona)</t>
+          <t>Sin Seminario (semana mechona)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -911,12 +889,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -951,12 +929,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -966,24 +944,16 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 1 y Revisión Certamen 1</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 1</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -999,12 +969,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1014,7 +984,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1039,12 +1009,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1054,7 +1024,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 1</t>
+          <t>Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
@@ -1079,12 +1049,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1094,7 +1064,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
+          <t>Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1119,12 +1089,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1134,24 +1104,16 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 2</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 3</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Control Modelos y Derivadas 2, 15 min</t>
-        </is>
-      </c>
+      <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1167,12 +1129,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1182,7 +1144,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1207,12 +1169,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1222,24 +1184,16 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 3</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 4</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Control Modelos y Derivadas 3, 15 min</t>
-        </is>
-      </c>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1255,12 +1209,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1270,7 +1224,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Modelos y Derivadas 5</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1295,12 +1249,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1310,24 +1264,16 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+          <t>Modelos y Derivadas 5</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Control Modelos y Derivadas 4, 15 min</t>
-        </is>
-      </c>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1343,12 +1289,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1370,44 +1316,44 @@
       <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="9" t="n">
         <v>46163</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Sección 2</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Sin clases (Feriado)</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Semana Receso</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Día de las Glorias Navales</t>
         </is>
@@ -1427,12 +1373,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1467,12 +1413,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1482,24 +1428,16 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
+          <t>Teórico Linealización de Modelos</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 2</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1515,12 +1453,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1530,7 +1468,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Linealización de modelos</t>
+          <t>Revisión Certamen 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1555,12 +1493,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1573,21 +1511,13 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo práctico</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Trabajo Práctico</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1603,12 +1533,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1643,12 +1573,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1683,12 +1613,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1723,12 +1653,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1741,21 +1671,13 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Control Trigonometría y Vectores 2, 15 min</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1771,12 +1693,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1811,12 +1733,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1829,21 +1751,13 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Control Trigonometría y Vectores 3, 15 min</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1859,12 +1773,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1899,123 +1813,115 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Seminario</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Sin Actividad (semana de certamen 3)</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>JCS</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
           <t>08:30–10:00</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Sección 2</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Seminario</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 3</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Certamen</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo autónomo</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo Autónomo</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>No hay clases (trabajo autónomo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo autónomo</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Revisión Certamen 3</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Certamen 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B34" s="13" t="n">
-        <v>46211</v>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>15:00–16:30</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>Sección 2</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo autónomo</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo Autónomo</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="J34" s="12" t="inlineStr">
-        <is>
-          <t>No hay clases (trabajo autónomo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B35" s="13" t="n">
-        <v>46212</v>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>Sección 2</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo autónomo</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>Trabajo Autónomo</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>JCS</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>No hay clases (trabajo autónomo).</t>
         </is>
@@ -2035,12 +1941,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2062,48 +1968,44 @@
       <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" s="9" t="n">
         <v>46219</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>08:30–10:00</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Sección 2</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>15:00–16:30</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>Sin clases (Feriado)</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Virgen del Carmen</t>
         </is>
@@ -2123,12 +2025,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>15:00–16:30</t>
+          <t>08:30–10:00</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2163,12 +2065,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>08:30–10:00</t>
+          <t>15:00–16:30</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2181,21 +2083,13 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Examen</t>
-        </is>
-      </c>
+      <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>JCS</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Examen 2</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J39"/>

--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -499,7 +499,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -590,7 +590,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -630,7 +630,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -670,7 +670,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -710,7 +710,7 @@
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
@@ -750,7 +750,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -790,7 +790,7 @@
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
@@ -830,7 +830,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -870,7 +870,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -910,7 +910,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -950,7 +950,7 @@
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
@@ -990,7 +990,7 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1514,7 +1514,7 @@
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -1554,7 +1554,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
@@ -1962,7 +1962,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       <c r="H37" s="8" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2046,7 +2046,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>TY, MB, GM, XX</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>

--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -109,18 +114,19 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,9 +504,9 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -707,13 +713,21 @@
           <t>Lógica 2</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Control lógica 2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -787,13 +801,21 @@
           <t>Lógica 3</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Control lógica 3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -907,13 +929,21 @@
           <t>Certamen 1</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1107,13 +1137,21 @@
           <t>Modelos y Derivadas 3</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1187,13 +1225,21 @@
           <t>Modelos y Derivadas 4</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1267,13 +1313,21 @@
           <t>Modelos y Derivadas 5</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Control Modelos y Derivadas 4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1316,44 +1370,44 @@
       <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>46163</v>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>15:00–16:30</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Sin clases (Feriado)</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Semana Receso</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Día de las Glorias Navales</t>
         </is>
@@ -1391,13 +1445,21 @@
           <t>Certamen 2</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1511,13 +1573,21 @@
           <t>Linealización de modelos</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo práctico</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Trabajo Práctico</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1671,13 +1741,21 @@
           <t>Trigonometría y Vectores 2</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1751,13 +1829,21 @@
           <t>Trigonometría y Vectores 3</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Control Trigonometría y Vectores 3</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1791,13 +1877,21 @@
           <t>Certamen 3</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Certamen</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Certamen 3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1840,88 +1934,88 @@
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>46211</v>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>08:30–10:00</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Trabajo autónomo</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Trabajo Autónomo</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr"/>
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>No hay clases (trabajo autónomo).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>46212</v>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>15:00–16:30</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>Trabajo autónomo</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Revisión Certamen 3</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr"/>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr"/>
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>No hay clases (trabajo autónomo).</t>
         </is>
@@ -1959,53 +2053,61 @@
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Examen 1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="10" t="n">
         <v>46219</v>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>15:00–16:30</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Sección 1</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Sección 1</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Sin clases (Feriado)</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Examen Primera Oportunidad</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>TY, MB, GM, XX</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Virgen del Carmen</t>
         </is>
@@ -2043,13 +2145,21 @@
           <t>Examen Segunda Oportunidad</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Examen 2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">

--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -636,7 +636,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -980,7 +980,7 @@
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1664,7 +1664,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
       <c r="H35" s="12" t="inlineStr"/>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -2104,7 +2104,7 @@
       <c r="H37" s="9" t="inlineStr"/>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -2196,7 +2196,7 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>TY, MB, GM, XX</t>
+          <t>TY, MB, GM, GF</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>

--- a/data/tecnologia_medica/calendario.xlsx
+++ b/data/tecnologia_medica/calendario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$39</definedName>
